--- a/data/trans_orig/POLIPATOLOGIA_5-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_5-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas en 2007</t>
+          <t>Población con cinco o más enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60586</t>
+          <t>60412</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91876</t>
+          <t>91787</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>151329</t>
+          <t>148484</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>197658</t>
+          <t>198498</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>220966</t>
+          <t>219334</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>277858</t>
+          <t>278627</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>939847</t>
+          <t>939936</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>971137</t>
+          <t>971311</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1117455</t>
+          <t>1116615</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1163784</t>
+          <t>1166629</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2068977</t>
+          <t>2068208</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2125869</t>
+          <t>2127501</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16760</t>
+          <t>17145</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>38402</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34606</t>
+          <t>33089</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60791</t>
+          <t>61733</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>55251</t>
+          <t>55700</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89375</t>
+          <t>88988</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1655292</t>
+          <t>1655011</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1676653</t>
+          <t>1676268</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1526882</t>
+          <t>1525940</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1553067</t>
+          <t>1554584</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3191711</t>
+          <t>3192098</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3225835</t>
+          <t>3225386</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19925</t>
+          <t>20368</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16004</t>
+          <t>15440</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11909</t>
+          <t>12391</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31584</t>
+          <t>30527</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>531483</t>
+          <t>531040</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545465</t>
+          <t>545287</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>460408</t>
+          <t>460972</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>472420</t>
+          <t>472672</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>996236</t>
+          <t>997293</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1015911</t>
+          <t>1015429</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92695</t>
+          <t>94626</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>134837</t>
+          <t>136121</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>198422</t>
+          <t>199560</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>260679</t>
+          <t>258014</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>306644</t>
+          <t>303891</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>378429</t>
+          <t>374096</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3141706</t>
+          <t>3140422</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3183848</t>
+          <t>3181917</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3118518</t>
+          <t>3121183</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3180775</t>
+          <t>3179637</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6277312</t>
+          <t>6281645</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6349097</t>
+          <t>6351850</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas en 2012</t>
+          <t>Población con cinco o más enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77395</t>
+          <t>76755</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>117024</t>
+          <t>116813</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>239365</t>
+          <t>238740</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>301048</t>
+          <t>302142</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>325218</t>
+          <t>330948</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>400592</t>
+          <t>399717</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>857619</t>
+          <t>857830</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>897248</t>
+          <t>897888</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1036749</t>
+          <t>1035655</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1098432</t>
+          <t>1099057</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1911848</t>
+          <t>1912723</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1987222</t>
+          <t>1981492</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,69%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19556</t>
+          <t>19256</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39971</t>
+          <t>40408</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51047</t>
+          <t>52390</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86508</t>
+          <t>87120</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76995</t>
+          <t>77009</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119262</t>
+          <t>118137</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1923986</t>
+          <t>1923549</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1944401</t>
+          <t>1944701</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1671295</t>
+          <t>1670683</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1706756</t>
+          <t>1705413</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3602498</t>
+          <t>3603623</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3644765</t>
+          <t>3644751</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>15295</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25595</t>
+          <t>25436</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>13317</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35520</t>
+          <t>35148</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>466760</t>
+          <t>465886</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>479228</t>
+          <t>479230</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>433036</t>
+          <t>433195</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>449607</t>
+          <t>450036</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>904293</t>
+          <t>904665</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>926708</t>
+          <t>926496</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>108066</t>
+          <t>107719</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>155514</t>
+          <t>154780</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>317635</t>
+          <t>316033</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>392157</t>
+          <t>386592</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>437582</t>
+          <t>438847</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>528368</t>
+          <t>526698</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3264268</t>
+          <t>3265002</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3311716</t>
+          <t>3312063</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3162073</t>
+          <t>3167638</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3236595</t>
+          <t>3238197</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6445644</t>
+          <t>6447314</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6536430</t>
+          <t>6535165</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas en 2016</t>
+          <t>Población con cinco o más enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55395</t>
+          <t>56073</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85224</t>
+          <t>86744</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>184385</t>
+          <t>183515</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>240598</t>
+          <t>238319</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>249262</t>
+          <t>250807</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>314820</t>
+          <t>314254</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>669123</t>
+          <t>667603</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>698952</t>
+          <t>698274</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>754062</t>
+          <t>756341</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>810275</t>
+          <t>811145</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1434187</t>
+          <t>1434753</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1499745</t>
+          <t>1498200</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,66%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27828</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52820</t>
+          <t>52938</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>97205</t>
+          <t>98175</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>141631</t>
+          <t>144202</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>132666</t>
+          <t>131849</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>182249</t>
+          <t>181872</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2023565</t>
+          <t>2023447</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2048557</t>
+          <t>2048373</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1846669</t>
+          <t>1844098</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1891095</t>
+          <t>1890125</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3882436</t>
+          <t>3882813</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3932019</t>
+          <t>3932836</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20718</t>
+          <t>19727</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10024</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27730</t>
+          <t>27980</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18599</t>
+          <t>18542</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42762</t>
+          <t>42335</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>526168</t>
+          <t>527159</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>541301</t>
+          <t>541773</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>521410</t>
+          <t>521160</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>539116</t>
+          <t>539031</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1053265</t>
+          <t>1053692</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1077428</t>
+          <t>1077485</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98077</t>
+          <t>100279</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>141177</t>
+          <t>141374</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>312116</t>
+          <t>309929</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>386867</t>
+          <t>382325</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>418556</t>
+          <t>422567</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>509824</t>
+          <t>508806</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3236441</t>
+          <t>3236244</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3279541</t>
+          <t>3277339</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3145233</t>
+          <t>3149775</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3219984</t>
+          <t>3222171</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6399894</t>
+          <t>6400912</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6491162</t>
+          <t>6487151</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas en 2023</t>
+          <t>Población con cinco o más enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97821</t>
+          <t>99466</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>130204</t>
+          <t>131247</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>266217</t>
+          <t>264902</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>308204</t>
+          <t>306231</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>373210</t>
+          <t>374408</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>428140</t>
+          <t>428171</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>384734</t>
+          <t>383691</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>417117</t>
+          <t>415472</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>447304</t>
+          <t>449277</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>489291</t>
+          <t>490606</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>842306</t>
+          <t>842275</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>897236</t>
+          <t>896038</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,53%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90706</t>
+          <t>93607</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>159970</t>
+          <t>161031</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>232432</t>
+          <t>231864</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>928365</t>
+          <t>855414</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>355769</t>
+          <t>351194</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1248129</t>
+          <t>1212740</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2130357</t>
+          <t>2129296</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2199621</t>
+          <t>2196720</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1309458</t>
+          <t>1382409</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2005391</t>
+          <t>2005959</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3280021</t>
+          <t>3315410</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4172381</t>
+          <t>4176956</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,24%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17861</t>
+          <t>18252</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35724</t>
+          <t>35897</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44919</t>
+          <t>45244</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68920</t>
+          <t>69278</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67097</t>
+          <t>67919</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95821</t>
+          <t>96988</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>610899</t>
+          <t>610726</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>628762</t>
+          <t>628371</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>591543</t>
+          <t>591185</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>615544</t>
+          <t>615219</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1211265</t>
+          <t>1210098</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1239989</t>
+          <t>1239167</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,8%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>209582</t>
+          <t>216377</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>309959</t>
+          <t>306954</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>581056</t>
+          <t>581887</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1312265</t>
+          <t>1303859</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>830319</t>
+          <t>825731</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1676120</t>
+          <t>1634296</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3141930</t>
+          <t>3144935</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3242307</t>
+          <t>3235512</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2341529</t>
+          <t>2349935</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3072738</t>
+          <t>3071907</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5429563</t>
+          <t>5471387</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6275364</t>
+          <t>6279952</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/POLIPATOLOGIA_5-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_5-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60412</t>
+          <t>59812</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91787</t>
+          <t>91850</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>148484</t>
+          <t>151364</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>198498</t>
+          <t>199749</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>219334</t>
+          <t>218259</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>278627</t>
+          <t>277089</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>939936</t>
+          <t>939873</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>971311</t>
+          <t>971911</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1116615</t>
+          <t>1115364</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1166629</t>
+          <t>1163749</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2068208</t>
+          <t>2069746</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2127501</t>
+          <t>2128576</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,7%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17145</t>
+          <t>16634</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38402</t>
+          <t>37702</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33089</t>
+          <t>34167</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61733</t>
+          <t>62547</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>55700</t>
+          <t>57240</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>88988</t>
+          <t>89539</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1655011</t>
+          <t>1655711</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1676268</t>
+          <t>1676779</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1525940</t>
+          <t>1525126</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1554584</t>
+          <t>1553506</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3192098</t>
+          <t>3191547</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3225386</t>
+          <t>3223846</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>6198</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20368</t>
+          <t>20856</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15440</t>
+          <t>16831</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12391</t>
+          <t>12349</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30527</t>
+          <t>30819</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>531040</t>
+          <t>530552</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545287</t>
+          <t>545210</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>460972</t>
+          <t>459581</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>472672</t>
+          <t>472311</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>997293</t>
+          <t>997001</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1015429</t>
+          <t>1015471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94626</t>
+          <t>92334</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>136121</t>
+          <t>132324</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>199560</t>
+          <t>198888</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>258014</t>
+          <t>259829</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>303891</t>
+          <t>303623</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>374096</t>
+          <t>375812</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3140422</t>
+          <t>3144219</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3181917</t>
+          <t>3184209</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3121183</t>
+          <t>3119368</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3179637</t>
+          <t>3180309</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6281645</t>
+          <t>6279929</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6351850</t>
+          <t>6352118</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76755</t>
+          <t>78228</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>116813</t>
+          <t>116992</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>238740</t>
+          <t>238176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>302142</t>
+          <t>299509</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>330948</t>
+          <t>330445</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>399717</t>
+          <t>406958</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,6%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>857830</t>
+          <t>857651</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>897888</t>
+          <t>896415</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1035655</t>
+          <t>1038288</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1099057</t>
+          <t>1099621</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1912723</t>
+          <t>1905482</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1981492</t>
+          <t>1981995</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19256</t>
+          <t>18570</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40408</t>
+          <t>40107</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,82 +2694,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>67930</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>51071</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>87003</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>95926</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>76681</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>116613</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>2,06%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>67930</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>52390</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>87120</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>4,96%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>95926</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>77009</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>118137</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1923549</t>
+          <t>1923850</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1944701</t>
+          <t>1945387</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,82 +2807,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>97,96%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1689873</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1670800</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1706732</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>96,14%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>95,05%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>97,09%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>3405</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>3625834</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>3605147</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3645079</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>96,87%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>97,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1576</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1689873</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1670683</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1705413</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,14%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>95,04%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>97,02%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>3405</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>3625834</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>3603623</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3644751</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>96,83%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15295</t>
+          <t>18009</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8595</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25436</t>
+          <t>26028</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13317</t>
+          <t>12829</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35148</t>
+          <t>34583</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>465886</t>
+          <t>463172</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>479230</t>
+          <t>479197</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>433195</t>
+          <t>432603</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>450036</t>
+          <t>449699</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>904665</t>
+          <t>905230</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>926496</t>
+          <t>926984</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>107719</t>
+          <t>108022</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>154780</t>
+          <t>153204</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>316033</t>
+          <t>315542</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>386592</t>
+          <t>388483</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>438847</t>
+          <t>437388</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>526698</t>
+          <t>528045</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3265002</t>
+          <t>3266578</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3312063</t>
+          <t>3311760</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3167638</t>
+          <t>3165747</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3238197</t>
+          <t>3238688</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6447314</t>
+          <t>6445967</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6535165</t>
+          <t>6536624</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56073</t>
+          <t>56687</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86744</t>
+          <t>85225</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>183515</t>
+          <t>184091</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>238319</t>
+          <t>239867</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>250807</t>
+          <t>249381</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>314254</t>
+          <t>314128</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>667603</t>
+          <t>669122</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>698274</t>
+          <t>697660</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>756341</t>
+          <t>754793</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>811145</t>
+          <t>810569</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1434753</t>
+          <t>1434879</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1498200</t>
+          <t>1499626</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,74%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>25852</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52938</t>
+          <t>52092</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>98175</t>
+          <t>96543</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>144202</t>
+          <t>140376</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>131849</t>
+          <t>131660</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>181872</t>
+          <t>183638</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2023447</t>
+          <t>2024293</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2048373</t>
+          <t>2050533</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1844098</t>
+          <t>1847924</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1890125</t>
+          <t>1891757</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3882813</t>
+          <t>3881047</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3932836</t>
+          <t>3933025</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19727</t>
+          <t>20459</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27980</t>
+          <t>29068</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18542</t>
+          <t>17322</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42335</t>
+          <t>41222</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>527159</t>
+          <t>526427</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>541773</t>
+          <t>541674</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>521160</t>
+          <t>520072</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>539031</t>
+          <t>539115</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1053692</t>
+          <t>1054805</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1077485</t>
+          <t>1078705</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100279</t>
+          <t>102511</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>141374</t>
+          <t>142734</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>309929</t>
+          <t>310604</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>382325</t>
+          <t>388201</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>422567</t>
+          <t>421702</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>508806</t>
+          <t>510001</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3236244</t>
+          <t>3234884</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3277339</t>
+          <t>3275107</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3149775</t>
+          <t>3143899</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3222171</t>
+          <t>3221496</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6400912</t>
+          <t>6399717</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6487151</t>
+          <t>6488016</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>113857</t>
+          <t>120945</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99466</t>
+          <t>105711</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>131247</t>
+          <t>142543</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>286952</t>
+          <t>306519</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>264902</t>
+          <t>285277</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>306231</t>
+          <t>326852</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>400808</t>
+          <t>427463</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>374408</t>
+          <t>399697</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>428171</t>
+          <t>457750</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>401081</t>
+          <t>457584</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>383691</t>
+          <t>435986</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>415472</t>
+          <t>472818</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>468556</t>
+          <t>515519</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>449277</t>
+          <t>495186</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>490606</t>
+          <t>536761</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>869638</t>
+          <t>973104</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>842275</t>
+          <t>942817</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>896038</t>
+          <t>1000870</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>71,46%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>134150</t>
+          <t>145337</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>93607</t>
+          <t>125144</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>161031</t>
+          <t>167725</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>424697</t>
+          <t>241879</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>231864</t>
+          <t>220554</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>855414</t>
+          <t>266225</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>558846</t>
+          <t>387216</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>351194</t>
+          <t>358965</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1212740</t>
+          <t>421570</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2156177</t>
+          <t>2085229</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2129296</t>
+          <t>2062841</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2196720</t>
+          <t>2105422</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1813126</t>
+          <t>1929513</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1382409</t>
+          <t>1905167</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2005959</t>
+          <t>1950838</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3969304</t>
+          <t>4014743</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3315410</t>
+          <t>3980389</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4176956</t>
+          <t>4042994</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26034</t>
+          <t>29074</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18252</t>
+          <t>19839</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35897</t>
+          <t>40611</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>55317</t>
+          <t>62645</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45244</t>
+          <t>51191</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69278</t>
+          <t>75917</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>81350</t>
+          <t>91720</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67919</t>
+          <t>76739</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96988</t>
+          <t>109466</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>620589</t>
+          <t>682513</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>610726</t>
+          <t>670976</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>628371</t>
+          <t>691748</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>605146</t>
+          <t>672232</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>591185</t>
+          <t>658960</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>615219</t>
+          <t>683686</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1225736</t>
+          <t>1354744</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1210098</t>
+          <t>1336998</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1239167</t>
+          <t>1369725</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,69%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>274040</t>
+          <t>295356</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>216377</t>
+          <t>266412</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>306954</t>
+          <t>329322</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>766965</t>
+          <t>611043</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>581887</t>
+          <t>575568</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1303859</t>
+          <t>649216</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1041005</t>
+          <t>906399</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>825731</t>
+          <t>859214</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1634296</t>
+          <t>955798</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3177849</t>
+          <t>3225327</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3144935</t>
+          <t>3191361</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3235512</t>
+          <t>3254271</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2886829</t>
+          <t>3117264</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2349935</t>
+          <t>3079091</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3071907</t>
+          <t>3152739</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6064678</t>
+          <t>6342591</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5471387</t>
+          <t>6293192</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6279952</t>
+          <t>6389776</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,15%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
